--- a/web/public/forms/gy-nda.xlsx
+++ b/web/public/forms/gy-nda.xlsx
@@ -8,9 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="비밀유지계약서" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 예시" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'비밀유지계약서'!$A$1:$X$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$X$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -18,8 +20,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="6">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy&quot;년&quot; m&quot;월&quot; d&quot;일&quot;"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
+  </numFmts>
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,29 +36,56 @@
       <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="000F203F"/>
-      <sz val="10.5"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="00222222"/>
+      <color rgb="006B7280"/>
       <sz val="8.5"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="000F203F"/>
+      <color rgb="00111827"/>
       <sz val="19"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="000F203F"/>
+      <color rgb="001F2937"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="00222222"/>
+      <color rgb="00000000"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="001F2937"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="001F2937"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="001F2937"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="4">
@@ -65,12 +97,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F6F8FC"/>
+        <fgColor rgb="00F3F5F9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EEF3FB"/>
+        <fgColor rgb="00E8EEF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -84,23 +116,23 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </left>
       <right style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </right>
       <top style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -109,35 +141,53 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -533,15 +583,15 @@
     <col width="3.6" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵   |   k-conmap.com   무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">← 이 1행을 지우고 쓰셔도 됩니다   </t>
+          <t xml:space="preserve">← 이 1행을 지우고 쓰셔도 됩니다  </t>
         </is>
       </c>
     </row>
@@ -565,7 +615,7 @@
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="n"/>
-      <c r="G5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="n"/>
       <c r="H5" s="5" t="n"/>
       <c r="I5" s="5" t="n"/>
       <c r="J5" s="5" t="n"/>
@@ -595,7 +645,7 @@
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
-      <c r="G6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="n"/>
       <c r="H6" s="5" t="n"/>
       <c r="I6" s="5" t="n"/>
       <c r="J6" s="5" t="n"/>
@@ -625,7 +675,7 @@
       <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="inlineStr"/>
+      <c r="G7" s="6" t="n"/>
       <c r="H7" s="5" t="n"/>
       <c r="I7" s="5" t="n"/>
       <c r="J7" s="5" t="n"/>
@@ -644,7 +694,7 @@
       <c r="W7" s="5" t="n"/>
       <c r="X7" s="5" t="n"/>
     </row>
-    <row r="8" ht="24" customHeight="1">
+    <row r="8" ht="34" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  자료 반환·폐기 시기</t>
@@ -655,7 +705,7 @@
       <c r="D8" s="5" t="n"/>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
-      <c r="G8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="n"/>
       <c r="H8" s="5" t="n"/>
       <c r="I8" s="5" t="n"/>
       <c r="J8" s="5" t="n"/>
@@ -684,14 +734,14 @@
     </row>
     <row r="11" ht="6" customHeight="1"/>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>제1조 (비밀정보)</t>
         </is>
       </c>
     </row>
     <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>비밀정보란 갑이 을에게 제공하는 위 범위의 자료와 그로부터 알게 된 정보를 말한다. 이미 공개되었거나 을이 독자적으로 취득한 정보는 제외한다.</t>
         </is>
@@ -699,14 +749,14 @@
     </row>
     <row r="14" ht="4" customHeight="1"/>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>제2조 (비밀 유지)</t>
         </is>
       </c>
     </row>
     <row r="16" ht="43.5" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>을은 비밀정보를 위 목적 외에 사용하지 아니하며, 갑의 서면 동의 없이 제3자에게 제공하지 아니한다.</t>
         </is>
@@ -714,14 +764,14 @@
     </row>
     <row r="17" ht="4" customHeight="1"/>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>제3조 (관리)</t>
         </is>
       </c>
     </row>
     <row r="19" ht="43.5" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>을은 비밀정보를 선량한 관리자의 주의로 관리하고, 업무상 필요한 최소한의 임직원에게만 접근을 허용한다.</t>
         </is>
@@ -729,14 +779,14 @@
     </row>
     <row r="20" ht="4" customHeight="1"/>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>제4조 (반환·폐기)</t>
         </is>
       </c>
     </row>
     <row r="22" ht="43.5" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>을은 목적이 달성되거나 갑의 요구가 있는 때에는 위 시기에 비밀정보를 반환하거나 폐기하고 그 사실을 확인해 준다.</t>
         </is>
@@ -744,14 +794,14 @@
     </row>
     <row r="23" ht="4" customHeight="1"/>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="1" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>제5조 (유효기간)</t>
         </is>
       </c>
     </row>
     <row r="25" ht="29" customHeight="1">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>이 계약의 효력은 위 기간 동안 유지된다.</t>
         </is>
@@ -759,14 +809,14 @@
     </row>
     <row r="26" ht="4" customHeight="1"/>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="1" t="inlineStr">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>제6조 (위반의 책임)</t>
         </is>
       </c>
     </row>
     <row r="28" ht="43.5" customHeight="1">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>을이 이 계약을 위반하여 갑에게 손해를 입힌 때에는 그 손해를 배상한다.</t>
         </is>
@@ -774,14 +824,14 @@
     </row>
     <row r="29" ht="4" customHeight="1"/>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="1" t="inlineStr">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>제7조 (분쟁의 해결)</t>
         </is>
       </c>
     </row>
     <row r="31" ht="43.5" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>분쟁은 협의로 해결하되, 협의가 되지 아니한 때에는 관할 법원의 판결에 따른다.</t>
         </is>
@@ -790,13 +840,13 @@
     <row r="32" ht="4" customHeight="1"/>
     <row r="33" ht="6" customHeight="1"/>
     <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="9" t="inlineStr">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
       <c r="B34" s="5" t="n"/>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="C34" s="10" t="inlineStr">
         <is>
           <t>상호(성명)</t>
         </is>
@@ -805,7 +855,7 @@
       <c r="E34" s="5" t="n"/>
       <c r="F34" s="5" t="n"/>
       <c r="G34" s="5" t="n"/>
-      <c r="H34" s="9" t="inlineStr">
+      <c r="H34" s="10" t="inlineStr">
         <is>
           <t>사업자등록번호</t>
         </is>
@@ -813,14 +863,14 @@
       <c r="I34" s="5" t="n"/>
       <c r="J34" s="5" t="n"/>
       <c r="K34" s="5" t="n"/>
-      <c r="L34" s="9" t="inlineStr">
+      <c r="L34" s="10" t="inlineStr">
         <is>
           <t>대표자</t>
         </is>
       </c>
       <c r="M34" s="5" t="n"/>
       <c r="N34" s="5" t="n"/>
-      <c r="O34" s="9" t="inlineStr">
+      <c r="O34" s="10" t="inlineStr">
         <is>
           <t>주소</t>
         </is>
@@ -831,7 +881,7 @@
       <c r="S34" s="5" t="n"/>
       <c r="T34" s="5" t="n"/>
       <c r="U34" s="5" t="n"/>
-      <c r="V34" s="9" t="inlineStr">
+      <c r="V34" s="10" t="inlineStr">
         <is>
           <t>연락처</t>
         </is>
@@ -840,59 +890,67 @@
       <c r="X34" s="5" t="n"/>
     </row>
     <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="10" t="inlineStr"/>
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>갑</t>
+        </is>
+      </c>
       <c r="B35" s="5" t="n"/>
-      <c r="C35" s="10" t="inlineStr"/>
+      <c r="C35" s="11" t="n"/>
       <c r="D35" s="5" t="n"/>
       <c r="E35" s="5" t="n"/>
       <c r="F35" s="5" t="n"/>
       <c r="G35" s="5" t="n"/>
-      <c r="H35" s="10" t="inlineStr"/>
+      <c r="H35" s="11" t="n"/>
       <c r="I35" s="5" t="n"/>
       <c r="J35" s="5" t="n"/>
       <c r="K35" s="5" t="n"/>
-      <c r="L35" s="10" t="inlineStr"/>
+      <c r="L35" s="11" t="n"/>
       <c r="M35" s="5" t="n"/>
       <c r="N35" s="5" t="n"/>
-      <c r="O35" s="10" t="inlineStr"/>
+      <c r="O35" s="12" t="n"/>
       <c r="P35" s="5" t="n"/>
       <c r="Q35" s="5" t="n"/>
       <c r="R35" s="5" t="n"/>
       <c r="S35" s="5" t="n"/>
       <c r="T35" s="5" t="n"/>
       <c r="U35" s="5" t="n"/>
-      <c r="V35" s="10" t="inlineStr"/>
+      <c r="V35" s="11" t="n"/>
       <c r="W35" s="5" t="n"/>
       <c r="X35" s="5" t="n"/>
     </row>
     <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="10" t="inlineStr"/>
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>을</t>
+        </is>
+      </c>
       <c r="B36" s="5" t="n"/>
-      <c r="C36" s="10" t="inlineStr"/>
+      <c r="C36" s="11" t="n"/>
       <c r="D36" s="5" t="n"/>
       <c r="E36" s="5" t="n"/>
       <c r="F36" s="5" t="n"/>
       <c r="G36" s="5" t="n"/>
-      <c r="H36" s="10" t="inlineStr"/>
+      <c r="H36" s="11" t="n"/>
       <c r="I36" s="5" t="n"/>
       <c r="J36" s="5" t="n"/>
       <c r="K36" s="5" t="n"/>
-      <c r="L36" s="10" t="inlineStr"/>
+      <c r="L36" s="11" t="n"/>
       <c r="M36" s="5" t="n"/>
       <c r="N36" s="5" t="n"/>
-      <c r="O36" s="10" t="inlineStr"/>
+      <c r="O36" s="12" t="n"/>
       <c r="P36" s="5" t="n"/>
       <c r="Q36" s="5" t="n"/>
       <c r="R36" s="5" t="n"/>
       <c r="S36" s="5" t="n"/>
       <c r="T36" s="5" t="n"/>
       <c r="U36" s="5" t="n"/>
-      <c r="V36" s="10" t="inlineStr"/>
+      <c r="V36" s="11" t="n"/>
       <c r="W36" s="5" t="n"/>
       <c r="X36" s="5" t="n"/>
     </row>
     <row r="37" ht="6" customHeight="1"/>
-    <row r="38" ht="26" customHeight="1">
+    <row r="38" ht="34" customHeight="1">
       <c r="A38" s="7" t="inlineStr">
         <is>
           <t>※ 이 계약서는 일반 양식입니다. 실제 체결 전에 반드시 검토를 받으시고, 정부가 고시한 표준계약서가 있는 계약은 그 원문을 사용하시는 편이 안전합니다.</t>
@@ -902,47 +960,59 @@
     <row r="39" ht="6" customHeight="1"/>
     <row r="40" ht="10" customHeight="1"/>
     <row r="41" ht="26" customHeight="1">
-      <c r="A41" s="11" t="inlineStr">
-        <is>
-          <t>년        월        일</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="K42" s="12" t="inlineStr">
+      <c r="A41" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          년        월        일</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="14" t="inlineStr"/>
+      <c r="K42" s="15" t="inlineStr">
         <is>
           <t>갑 (정보제공자)</t>
         </is>
       </c>
-      <c r="S42" s="11" t="inlineStr">
+      <c r="Q42" s="16" t="n"/>
+      <c r="U42" s="17" t="inlineStr">
         <is>
           <t>(서명 또는 인)</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="K43" s="12" t="inlineStr">
+    <row r="43" ht="24" customHeight="1">
+      <c r="A43" s="14" t="inlineStr"/>
+      <c r="K43" s="15" t="inlineStr">
         <is>
           <t>을 (정보수령자)</t>
         </is>
       </c>
-      <c r="S43" s="11" t="inlineStr">
+      <c r="Q43" s="16" t="n"/>
+      <c r="U43" s="17" t="inlineStr">
         <is>
           <t>(서명 또는 인)</t>
         </is>
       </c>
     </row>
     <row r="44" ht="6" customHeight="1"/>
-    <row r="47">
-      <c r="A47" s="13" t="inlineStr">
-        <is>
-          <t>발주기관이 정한 서식이 있으면 그 서식을 사용하세요. 이 줄과 1행은 인쇄 전에 지우셔도 됩니다.</t>
+    <row r="46" ht="34" customHeight="1">
+      <c r="A46" s="18" t="inlineStr">
+        <is>
+          <t>노란 칸 = 요율·기준값(발주기관 기준으로 고쳐 씀) · 옅은 하늘색 칸 = 자동 계산(지우지 마세요) · 뒤 시트에 «작성 예시» 가 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="19.5" customHeight="1">
+      <c r="A47" s="18" t="inlineStr">
+        <is>
+          <t>발주기관이 정한 서식이 있으면 그 서식을 쓰세요. 이 줄과 1행은 지워도 됩니다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="51">
+  <mergeCells count="56">
     <mergeCell ref="V34:X34"/>
+    <mergeCell ref="U42:X42"/>
     <mergeCell ref="C34:G34"/>
     <mergeCell ref="G7:X7"/>
     <mergeCell ref="A16:X16"/>
@@ -950,7 +1020,10 @@
     <mergeCell ref="A41:X41"/>
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="G6:X6"/>
+    <mergeCell ref="A43:J43"/>
     <mergeCell ref="L35:N35"/>
+    <mergeCell ref="A46:X46"/>
+    <mergeCell ref="K43:P43"/>
     <mergeCell ref="A18:X18"/>
     <mergeCell ref="A27:X27"/>
     <mergeCell ref="A3:X3"/>
@@ -959,16 +1032,18 @@
     <mergeCell ref="A12:X12"/>
     <mergeCell ref="V36:X36"/>
     <mergeCell ref="A5:F5"/>
+    <mergeCell ref="K42:P42"/>
     <mergeCell ref="H35:K35"/>
     <mergeCell ref="G5:X5"/>
     <mergeCell ref="A8:F8"/>
+    <mergeCell ref="Q43:T43"/>
     <mergeCell ref="A47:X47"/>
     <mergeCell ref="L34:N34"/>
     <mergeCell ref="O34:U34"/>
     <mergeCell ref="A22:X22"/>
+    <mergeCell ref="Q42:T42"/>
     <mergeCell ref="A34:B34"/>
     <mergeCell ref="O36:U36"/>
-    <mergeCell ref="K43:R43"/>
     <mergeCell ref="L36:N36"/>
     <mergeCell ref="A38:X38"/>
     <mergeCell ref="H34:K34"/>
@@ -976,25 +1051,606 @@
     <mergeCell ref="A28:X28"/>
     <mergeCell ref="A19:X19"/>
     <mergeCell ref="C36:G36"/>
-    <mergeCell ref="K42:R42"/>
     <mergeCell ref="A13:X13"/>
     <mergeCell ref="A31:X31"/>
     <mergeCell ref="A35:B35"/>
     <mergeCell ref="H36:K36"/>
-    <mergeCell ref="S43:X43"/>
     <mergeCell ref="A30:X30"/>
     <mergeCell ref="O35:U35"/>
     <mergeCell ref="A24:X24"/>
-    <mergeCell ref="S42:X42"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A15:X15"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="V35:X35"/>
     <mergeCell ref="M1:X1"/>
+    <mergeCell ref="U43:X43"/>
+    <mergeCell ref="A42:J42"/>
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="G8:X8"/>
   </mergeCells>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00F59E0B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:X46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3.6" customWidth="1" min="1" max="1"/>
+    <col width="3.6" customWidth="1" min="2" max="2"/>
+    <col width="3.6" customWidth="1" min="3" max="3"/>
+    <col width="3.6" customWidth="1" min="4" max="4"/>
+    <col width="3.6" customWidth="1" min="5" max="5"/>
+    <col width="3.6" customWidth="1" min="6" max="6"/>
+    <col width="3.6" customWidth="1" min="7" max="7"/>
+    <col width="3.6" customWidth="1" min="8" max="8"/>
+    <col width="3.6" customWidth="1" min="9" max="9"/>
+    <col width="3.6" customWidth="1" min="10" max="10"/>
+    <col width="3.6" customWidth="1" min="11" max="11"/>
+    <col width="3.6" customWidth="1" min="12" max="12"/>
+    <col width="3.6" customWidth="1" min="13" max="13"/>
+    <col width="3.6" customWidth="1" min="14" max="14"/>
+    <col width="3.6" customWidth="1" min="15" max="15"/>
+    <col width="3.6" customWidth="1" min="16" max="16"/>
+    <col width="3.6" customWidth="1" min="17" max="17"/>
+    <col width="3.6" customWidth="1" min="18" max="18"/>
+    <col width="3.6" customWidth="1" min="19" max="19"/>
+    <col width="3.6" customWidth="1" min="20" max="20"/>
+    <col width="3.6" customWidth="1" min="21" max="21"/>
+    <col width="3.6" customWidth="1" min="22" max="22"/>
+    <col width="3.6" customWidth="1" min="23" max="23"/>
+    <col width="3.6" customWidth="1" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+        </is>
+      </c>
+      <c r="M1" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="6" customHeight="1"/>
+    <row r="3" ht="38" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>비 밀 유 지 계 약 서</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="10" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  목    적</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>가나지구 배수로 정비공사 하도급 견적을 위한 설계도서 제공</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
+      <c r="Q5" s="5" t="n"/>
+      <c r="R5" s="5" t="n"/>
+      <c r="S5" s="5" t="n"/>
+      <c r="T5" s="5" t="n"/>
+      <c r="U5" s="5" t="n"/>
+      <c r="V5" s="5" t="n"/>
+      <c r="W5" s="5" t="n"/>
+      <c r="X5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  비밀정보의 범위</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>설계도면·내역서·단가 자료 등 갑이 비밀로 표시해 준 자료</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+      <c r="P6" s="5" t="n"/>
+      <c r="Q6" s="5" t="n"/>
+      <c r="R6" s="5" t="n"/>
+      <c r="S6" s="5" t="n"/>
+      <c r="T6" s="5" t="n"/>
+      <c r="U6" s="5" t="n"/>
+      <c r="V6" s="5" t="n"/>
+      <c r="W6" s="5" t="n"/>
+      <c r="X6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  유효 기간</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>계약일부터 2년</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+      <c r="P7" s="5" t="n"/>
+      <c r="Q7" s="5" t="n"/>
+      <c r="R7" s="5" t="n"/>
+      <c r="S7" s="5" t="n"/>
+      <c r="T7" s="5" t="n"/>
+      <c r="U7" s="5" t="n"/>
+      <c r="V7" s="5" t="n"/>
+      <c r="W7" s="5" t="n"/>
+      <c r="X7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  자료 반환·폐기 시기</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>견적 제출 후 30일 안 또는 갑이 요구할 때</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+      <c r="P8" s="5" t="n"/>
+      <c r="Q8" s="5" t="n"/>
+      <c r="R8" s="5" t="n"/>
+      <c r="S8" s="5" t="n"/>
+      <c r="T8" s="5" t="n"/>
+      <c r="U8" s="5" t="n"/>
+      <c r="V8" s="5" t="n"/>
+      <c r="W8" s="5" t="n"/>
+      <c r="X8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="6" customHeight="1"/>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>정보제공자(이하 「갑」)와 정보수령자(이하 「을」)는 다음과 같이 계약을 체결한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="6" customHeight="1"/>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>제1조 (비밀정보)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>비밀정보란 갑이 을에게 제공하는 위 범위의 자료와 그로부터 알게 된 정보를 말한다. 이미 공개되었거나 을이 독자적으로 취득한 정보는 제외한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="4" customHeight="1"/>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>제2조 (비밀 유지)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="43.5" customHeight="1">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>을은 비밀정보를 위 목적 외에 사용하지 아니하며, 갑의 서면 동의 없이 제3자에게 제공하지 아니한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="4" customHeight="1"/>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>제3조 (관리)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="43.5" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>을은 비밀정보를 선량한 관리자의 주의로 관리하고, 업무상 필요한 최소한의 임직원에게만 접근을 허용한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="4" customHeight="1"/>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>제4조 (반환·폐기)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="43.5" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>을은 목적이 달성되거나 갑의 요구가 있는 때에는 위 시기에 비밀정보를 반환하거나 폐기하고 그 사실을 확인해 준다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="4" customHeight="1"/>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>제5조 (유효기간)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="29" customHeight="1">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>이 계약의 효력은 위 기간 동안 유지된다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="4" customHeight="1"/>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>제6조 (위반의 책임)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="43.5" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>을이 이 계약을 위반하여 갑에게 손해를 입힌 때에는 그 손해를 배상한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="4" customHeight="1"/>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>제7조 (분쟁의 해결)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="43.5" customHeight="1">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>분쟁은 협의로 해결하되, 협의가 되지 아니한 때에는 관할 법원의 판결에 따른다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="4" customHeight="1"/>
+    <row r="33" ht="6" customHeight="1"/>
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n"/>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>상호(성명)</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="n"/>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="5" t="n"/>
+      <c r="H34" s="10" t="inlineStr">
+        <is>
+          <t>사업자등록번호</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="n"/>
+      <c r="J34" s="5" t="n"/>
+      <c r="K34" s="5" t="n"/>
+      <c r="L34" s="10" t="inlineStr">
+        <is>
+          <t>대표자</t>
+        </is>
+      </c>
+      <c r="M34" s="5" t="n"/>
+      <c r="N34" s="5" t="n"/>
+      <c r="O34" s="10" t="inlineStr">
+        <is>
+          <t>주소</t>
+        </is>
+      </c>
+      <c r="P34" s="5" t="n"/>
+      <c r="Q34" s="5" t="n"/>
+      <c r="R34" s="5" t="n"/>
+      <c r="S34" s="5" t="n"/>
+      <c r="T34" s="5" t="n"/>
+      <c r="U34" s="5" t="n"/>
+      <c r="V34" s="10" t="inlineStr">
+        <is>
+          <t>연락처</t>
+        </is>
+      </c>
+      <c r="W34" s="5" t="n"/>
+      <c r="X34" s="5" t="n"/>
+    </row>
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>갑</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n"/>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>예시건설(주)</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="n"/>
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="5" t="n"/>
+      <c r="G35" s="5" t="n"/>
+      <c r="H35" s="11" t="inlineStr">
+        <is>
+          <t>000-00-00000</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="n"/>
+      <c r="J35" s="5" t="n"/>
+      <c r="K35" s="5" t="n"/>
+      <c r="L35" s="11" t="inlineStr">
+        <is>
+          <t>홍길동</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="n"/>
+      <c r="N35" s="5" t="n"/>
+      <c r="O35" s="12" t="inlineStr">
+        <is>
+          <t>가나시 마바로 45, 2층</t>
+        </is>
+      </c>
+      <c r="P35" s="5" t="n"/>
+      <c r="Q35" s="5" t="n"/>
+      <c r="R35" s="5" t="n"/>
+      <c r="S35" s="5" t="n"/>
+      <c r="T35" s="5" t="n"/>
+      <c r="U35" s="5" t="n"/>
+      <c r="V35" s="11" t="inlineStr">
+        <is>
+          <t>000-000-0000</t>
+        </is>
+      </c>
+      <c r="W35" s="5" t="n"/>
+      <c r="X35" s="5" t="n"/>
+    </row>
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>을</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n"/>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>(주)예시토건</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="n"/>
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="5" t="n"/>
+      <c r="G36" s="5" t="n"/>
+      <c r="H36" s="11" t="inlineStr">
+        <is>
+          <t>000-00-00000</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="n"/>
+      <c r="J36" s="5" t="n"/>
+      <c r="K36" s="5" t="n"/>
+      <c r="L36" s="11" t="inlineStr">
+        <is>
+          <t>나대표</t>
+        </is>
+      </c>
+      <c r="M36" s="5" t="n"/>
+      <c r="N36" s="5" t="n"/>
+      <c r="O36" s="12" t="inlineStr">
+        <is>
+          <t>다라시 가나로 12</t>
+        </is>
+      </c>
+      <c r="P36" s="5" t="n"/>
+      <c r="Q36" s="5" t="n"/>
+      <c r="R36" s="5" t="n"/>
+      <c r="S36" s="5" t="n"/>
+      <c r="T36" s="5" t="n"/>
+      <c r="U36" s="5" t="n"/>
+      <c r="V36" s="11" t="inlineStr">
+        <is>
+          <t>000-000-0000</t>
+        </is>
+      </c>
+      <c r="W36" s="5" t="n"/>
+      <c r="X36" s="5" t="n"/>
+    </row>
+    <row r="37" ht="6" customHeight="1"/>
+    <row r="38" ht="34" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>※ 이 계약서는 일반 양식입니다. 실제 체결 전에 반드시 검토를 받으시고, 정부가 고시한 표준계약서가 있는 계약은 그 원문을 사용하시는 편이 안전합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="6" customHeight="1"/>
+    <row r="40" ht="10" customHeight="1"/>
+    <row r="41" ht="26" customHeight="1">
+      <c r="A41" s="13" t="n">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="14" t="inlineStr"/>
+      <c r="K42" s="15" t="inlineStr">
+        <is>
+          <t>갑 (정보제공자)</t>
+        </is>
+      </c>
+      <c r="Q42" s="16" t="inlineStr">
+        <is>
+          <t>홍길동</t>
+        </is>
+      </c>
+      <c r="U42" s="17" t="inlineStr">
+        <is>
+          <t>(서명 또는 인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="24" customHeight="1">
+      <c r="A43" s="14" t="inlineStr"/>
+      <c r="K43" s="15" t="inlineStr">
+        <is>
+          <t>을 (정보수령자)</t>
+        </is>
+      </c>
+      <c r="Q43" s="16" t="inlineStr">
+        <is>
+          <t>나대표</t>
+        </is>
+      </c>
+      <c r="U43" s="17" t="inlineStr">
+        <is>
+          <t>(서명 또는 인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="6" customHeight="1"/>
+    <row r="46" ht="19.5" customHeight="1">
+      <c r="A46" s="18" t="inlineStr">
+        <is>
+          <t>이 시트는 작성 예시입니다(가상의 현장 · 이름 · 금액). 실제로는 앞 시트에 적으세요.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="55">
+    <mergeCell ref="V34:X34"/>
+    <mergeCell ref="U42:X42"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="G7:X7"/>
+    <mergeCell ref="A16:X16"/>
+    <mergeCell ref="A25:X25"/>
+    <mergeCell ref="A41:X41"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="G6:X6"/>
+    <mergeCell ref="A43:J43"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="A46:X46"/>
+    <mergeCell ref="K43:P43"/>
+    <mergeCell ref="A18:X18"/>
+    <mergeCell ref="A27:X27"/>
+    <mergeCell ref="A3:X3"/>
+    <mergeCell ref="A21:X21"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="A12:X12"/>
+    <mergeCell ref="V36:X36"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="K42:P42"/>
+    <mergeCell ref="H35:K35"/>
+    <mergeCell ref="G5:X5"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="Q43:T43"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="O34:U34"/>
+    <mergeCell ref="A22:X22"/>
+    <mergeCell ref="Q42:T42"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="O36:U36"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="A38:X38"/>
+    <mergeCell ref="H34:K34"/>
+    <mergeCell ref="A10:X10"/>
+    <mergeCell ref="A28:X28"/>
+    <mergeCell ref="A19:X19"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="A13:X13"/>
+    <mergeCell ref="A31:X31"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="H36:K36"/>
+    <mergeCell ref="A30:X30"/>
+    <mergeCell ref="O35:U35"/>
+    <mergeCell ref="A24:X24"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A15:X15"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="V35:X35"/>
+    <mergeCell ref="M1:X1"/>
+    <mergeCell ref="U43:X43"/>
+    <mergeCell ref="A42:J42"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G8:X8"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/web/public/forms/gy-nda.xlsx
+++ b/web/public/forms/gy-nda.xlsx
@@ -586,7 +586,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
@@ -1113,7 +1113,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="M1" s="19" t="inlineStr">

--- a/web/public/forms/gy-nda.xlsx
+++ b/web/public/forms/gy-nda.xlsx
@@ -8,11 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="비밀유지계약서" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 예시" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'비밀유지계약서'!$A$1:$X$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$X$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -132,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -185,9 +183,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -995,6 +990,7 @@
       </c>
     </row>
     <row r="44" ht="6" customHeight="1"/>
+    <row r="45"/>
     <row r="46" ht="34" customHeight="1">
       <c r="A46" s="18" t="inlineStr">
         <is>
@@ -1072,585 +1068,4 @@
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F59E0B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:X46"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="3.6" customWidth="1" min="1" max="1"/>
-    <col width="3.6" customWidth="1" min="2" max="2"/>
-    <col width="3.6" customWidth="1" min="3" max="3"/>
-    <col width="3.6" customWidth="1" min="4" max="4"/>
-    <col width="3.6" customWidth="1" min="5" max="5"/>
-    <col width="3.6" customWidth="1" min="6" max="6"/>
-    <col width="3.6" customWidth="1" min="7" max="7"/>
-    <col width="3.6" customWidth="1" min="8" max="8"/>
-    <col width="3.6" customWidth="1" min="9" max="9"/>
-    <col width="3.6" customWidth="1" min="10" max="10"/>
-    <col width="3.6" customWidth="1" min="11" max="11"/>
-    <col width="3.6" customWidth="1" min="12" max="12"/>
-    <col width="3.6" customWidth="1" min="13" max="13"/>
-    <col width="3.6" customWidth="1" min="14" max="14"/>
-    <col width="3.6" customWidth="1" min="15" max="15"/>
-    <col width="3.6" customWidth="1" min="16" max="16"/>
-    <col width="3.6" customWidth="1" min="17" max="17"/>
-    <col width="3.6" customWidth="1" min="18" max="18"/>
-    <col width="3.6" customWidth="1" min="19" max="19"/>
-    <col width="3.6" customWidth="1" min="20" max="20"/>
-    <col width="3.6" customWidth="1" min="21" max="21"/>
-    <col width="3.6" customWidth="1" min="22" max="22"/>
-    <col width="3.6" customWidth="1" min="23" max="23"/>
-    <col width="3.6" customWidth="1" min="24" max="24"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
-        </is>
-      </c>
-      <c r="M1" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="6" customHeight="1"/>
-    <row r="3" ht="38" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>비 밀 유 지 계 약 서</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="10" customHeight="1"/>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  목    적</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>가나지구 배수로 정비공사 하도급 견적을 위한 설계도서 제공</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="n"/>
-      <c r="L5" s="5" t="n"/>
-      <c r="M5" s="5" t="n"/>
-      <c r="N5" s="5" t="n"/>
-      <c r="O5" s="5" t="n"/>
-      <c r="P5" s="5" t="n"/>
-      <c r="Q5" s="5" t="n"/>
-      <c r="R5" s="5" t="n"/>
-      <c r="S5" s="5" t="n"/>
-      <c r="T5" s="5" t="n"/>
-      <c r="U5" s="5" t="n"/>
-      <c r="V5" s="5" t="n"/>
-      <c r="W5" s="5" t="n"/>
-      <c r="X5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  비밀정보의 범위</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>설계도면·내역서·단가 자료 등 갑이 비밀로 표시해 준 자료</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="n"/>
-      <c r="L6" s="5" t="n"/>
-      <c r="M6" s="5" t="n"/>
-      <c r="N6" s="5" t="n"/>
-      <c r="O6" s="5" t="n"/>
-      <c r="P6" s="5" t="n"/>
-      <c r="Q6" s="5" t="n"/>
-      <c r="R6" s="5" t="n"/>
-      <c r="S6" s="5" t="n"/>
-      <c r="T6" s="5" t="n"/>
-      <c r="U6" s="5" t="n"/>
-      <c r="V6" s="5" t="n"/>
-      <c r="W6" s="5" t="n"/>
-      <c r="X6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  유효 기간</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>계약일부터 2년</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="n"/>
-      <c r="L7" s="5" t="n"/>
-      <c r="M7" s="5" t="n"/>
-      <c r="N7" s="5" t="n"/>
-      <c r="O7" s="5" t="n"/>
-      <c r="P7" s="5" t="n"/>
-      <c r="Q7" s="5" t="n"/>
-      <c r="R7" s="5" t="n"/>
-      <c r="S7" s="5" t="n"/>
-      <c r="T7" s="5" t="n"/>
-      <c r="U7" s="5" t="n"/>
-      <c r="V7" s="5" t="n"/>
-      <c r="W7" s="5" t="n"/>
-      <c r="X7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  자료 반환·폐기 시기</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>견적 제출 후 30일 안 또는 갑이 요구할 때</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="n"/>
-      <c r="L8" s="5" t="n"/>
-      <c r="M8" s="5" t="n"/>
-      <c r="N8" s="5" t="n"/>
-      <c r="O8" s="5" t="n"/>
-      <c r="P8" s="5" t="n"/>
-      <c r="Q8" s="5" t="n"/>
-      <c r="R8" s="5" t="n"/>
-      <c r="S8" s="5" t="n"/>
-      <c r="T8" s="5" t="n"/>
-      <c r="U8" s="5" t="n"/>
-      <c r="V8" s="5" t="n"/>
-      <c r="W8" s="5" t="n"/>
-      <c r="X8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="6" customHeight="1"/>
-    <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>정보제공자(이하 「갑」)와 정보수령자(이하 「을」)는 다음과 같이 계약을 체결한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="6" customHeight="1"/>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>제1조 (비밀정보)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>비밀정보란 갑이 을에게 제공하는 위 범위의 자료와 그로부터 알게 된 정보를 말한다. 이미 공개되었거나 을이 독자적으로 취득한 정보는 제외한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="4" customHeight="1"/>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>제2조 (비밀 유지)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="43.5" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>을은 비밀정보를 위 목적 외에 사용하지 아니하며, 갑의 서면 동의 없이 제3자에게 제공하지 아니한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="4" customHeight="1"/>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>제3조 (관리)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="43.5" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>을은 비밀정보를 선량한 관리자의 주의로 관리하고, 업무상 필요한 최소한의 임직원에게만 접근을 허용한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="4" customHeight="1"/>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>제4조 (반환·폐기)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="43.5" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>을은 목적이 달성되거나 갑의 요구가 있는 때에는 위 시기에 비밀정보를 반환하거나 폐기하고 그 사실을 확인해 준다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="4" customHeight="1"/>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>제5조 (유효기간)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="29" customHeight="1">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>이 계약의 효력은 위 기간 동안 유지된다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="4" customHeight="1"/>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>제6조 (위반의 책임)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="43.5" customHeight="1">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>을이 이 계약을 위반하여 갑에게 손해를 입힌 때에는 그 손해를 배상한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="4" customHeight="1"/>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>제7조 (분쟁의 해결)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="43.5" customHeight="1">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t>분쟁은 협의로 해결하되, 협의가 되지 아니한 때에는 관할 법원의 판결에 따른다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="4" customHeight="1"/>
-    <row r="33" ht="6" customHeight="1"/>
-    <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="10" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="n"/>
-      <c r="C34" s="10" t="inlineStr">
-        <is>
-          <t>상호(성명)</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="5" t="n"/>
-      <c r="F34" s="5" t="n"/>
-      <c r="G34" s="5" t="n"/>
-      <c r="H34" s="10" t="inlineStr">
-        <is>
-          <t>사업자등록번호</t>
-        </is>
-      </c>
-      <c r="I34" s="5" t="n"/>
-      <c r="J34" s="5" t="n"/>
-      <c r="K34" s="5" t="n"/>
-      <c r="L34" s="10" t="inlineStr">
-        <is>
-          <t>대표자</t>
-        </is>
-      </c>
-      <c r="M34" s="5" t="n"/>
-      <c r="N34" s="5" t="n"/>
-      <c r="O34" s="10" t="inlineStr">
-        <is>
-          <t>주소</t>
-        </is>
-      </c>
-      <c r="P34" s="5" t="n"/>
-      <c r="Q34" s="5" t="n"/>
-      <c r="R34" s="5" t="n"/>
-      <c r="S34" s="5" t="n"/>
-      <c r="T34" s="5" t="n"/>
-      <c r="U34" s="5" t="n"/>
-      <c r="V34" s="10" t="inlineStr">
-        <is>
-          <t>연락처</t>
-        </is>
-      </c>
-      <c r="W34" s="5" t="n"/>
-      <c r="X34" s="5" t="n"/>
-    </row>
-    <row r="35" ht="32" customHeight="1">
-      <c r="A35" s="11" t="inlineStr">
-        <is>
-          <t>갑</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="n"/>
-      <c r="C35" s="11" t="inlineStr">
-        <is>
-          <t>예시건설(주)</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="n"/>
-      <c r="E35" s="5" t="n"/>
-      <c r="F35" s="5" t="n"/>
-      <c r="G35" s="5" t="n"/>
-      <c r="H35" s="11" t="inlineStr">
-        <is>
-          <t>000-00-00000</t>
-        </is>
-      </c>
-      <c r="I35" s="5" t="n"/>
-      <c r="J35" s="5" t="n"/>
-      <c r="K35" s="5" t="n"/>
-      <c r="L35" s="11" t="inlineStr">
-        <is>
-          <t>홍길동</t>
-        </is>
-      </c>
-      <c r="M35" s="5" t="n"/>
-      <c r="N35" s="5" t="n"/>
-      <c r="O35" s="12" t="inlineStr">
-        <is>
-          <t>가나시 마바로 45, 2층</t>
-        </is>
-      </c>
-      <c r="P35" s="5" t="n"/>
-      <c r="Q35" s="5" t="n"/>
-      <c r="R35" s="5" t="n"/>
-      <c r="S35" s="5" t="n"/>
-      <c r="T35" s="5" t="n"/>
-      <c r="U35" s="5" t="n"/>
-      <c r="V35" s="11" t="inlineStr">
-        <is>
-          <t>000-000-0000</t>
-        </is>
-      </c>
-      <c r="W35" s="5" t="n"/>
-      <c r="X35" s="5" t="n"/>
-    </row>
-    <row r="36" ht="32" customHeight="1">
-      <c r="A36" s="11" t="inlineStr">
-        <is>
-          <t>을</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="n"/>
-      <c r="C36" s="11" t="inlineStr">
-        <is>
-          <t>(주)예시토건</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="n"/>
-      <c r="E36" s="5" t="n"/>
-      <c r="F36" s="5" t="n"/>
-      <c r="G36" s="5" t="n"/>
-      <c r="H36" s="11" t="inlineStr">
-        <is>
-          <t>000-00-00000</t>
-        </is>
-      </c>
-      <c r="I36" s="5" t="n"/>
-      <c r="J36" s="5" t="n"/>
-      <c r="K36" s="5" t="n"/>
-      <c r="L36" s="11" t="inlineStr">
-        <is>
-          <t>나대표</t>
-        </is>
-      </c>
-      <c r="M36" s="5" t="n"/>
-      <c r="N36" s="5" t="n"/>
-      <c r="O36" s="12" t="inlineStr">
-        <is>
-          <t>다라시 가나로 12</t>
-        </is>
-      </c>
-      <c r="P36" s="5" t="n"/>
-      <c r="Q36" s="5" t="n"/>
-      <c r="R36" s="5" t="n"/>
-      <c r="S36" s="5" t="n"/>
-      <c r="T36" s="5" t="n"/>
-      <c r="U36" s="5" t="n"/>
-      <c r="V36" s="11" t="inlineStr">
-        <is>
-          <t>000-000-0000</t>
-        </is>
-      </c>
-      <c r="W36" s="5" t="n"/>
-      <c r="X36" s="5" t="n"/>
-    </row>
-    <row r="37" ht="6" customHeight="1"/>
-    <row r="38" ht="34" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>※ 이 계약서는 일반 양식입니다. 실제 체결 전에 반드시 검토를 받으시고, 정부가 고시한 표준계약서가 있는 계약은 그 원문을 사용하시는 편이 안전합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="6" customHeight="1"/>
-    <row r="40" ht="10" customHeight="1"/>
-    <row r="41" ht="26" customHeight="1">
-      <c r="A41" s="13" t="n">
-        <v>46294</v>
-      </c>
-    </row>
-    <row r="42" ht="24" customHeight="1">
-      <c r="A42" s="14" t="inlineStr"/>
-      <c r="K42" s="15" t="inlineStr">
-        <is>
-          <t>갑 (정보제공자)</t>
-        </is>
-      </c>
-      <c r="Q42" s="16" t="inlineStr">
-        <is>
-          <t>홍길동</t>
-        </is>
-      </c>
-      <c r="U42" s="17" t="inlineStr">
-        <is>
-          <t>(서명 또는 인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="24" customHeight="1">
-      <c r="A43" s="14" t="inlineStr"/>
-      <c r="K43" s="15" t="inlineStr">
-        <is>
-          <t>을 (정보수령자)</t>
-        </is>
-      </c>
-      <c r="Q43" s="16" t="inlineStr">
-        <is>
-          <t>나대표</t>
-        </is>
-      </c>
-      <c r="U43" s="17" t="inlineStr">
-        <is>
-          <t>(서명 또는 인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="6" customHeight="1"/>
-    <row r="46" ht="19.5" customHeight="1">
-      <c r="A46" s="18" t="inlineStr">
-        <is>
-          <t>이 시트는 작성 예시입니다(가상의 현장 · 이름 · 금액). 실제로는 앞 시트에 적으세요.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="55">
-    <mergeCell ref="V34:X34"/>
-    <mergeCell ref="U42:X42"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="G7:X7"/>
-    <mergeCell ref="A16:X16"/>
-    <mergeCell ref="A25:X25"/>
-    <mergeCell ref="A41:X41"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="G6:X6"/>
-    <mergeCell ref="A43:J43"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="A46:X46"/>
-    <mergeCell ref="K43:P43"/>
-    <mergeCell ref="A18:X18"/>
-    <mergeCell ref="A27:X27"/>
-    <mergeCell ref="A3:X3"/>
-    <mergeCell ref="A21:X21"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="A12:X12"/>
-    <mergeCell ref="V36:X36"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="K42:P42"/>
-    <mergeCell ref="H35:K35"/>
-    <mergeCell ref="G5:X5"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="Q43:T43"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="O34:U34"/>
-    <mergeCell ref="A22:X22"/>
-    <mergeCell ref="Q42:T42"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="O36:U36"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="A38:X38"/>
-    <mergeCell ref="H34:K34"/>
-    <mergeCell ref="A10:X10"/>
-    <mergeCell ref="A28:X28"/>
-    <mergeCell ref="A19:X19"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="A13:X13"/>
-    <mergeCell ref="A31:X31"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="H36:K36"/>
-    <mergeCell ref="A30:X30"/>
-    <mergeCell ref="O35:U35"/>
-    <mergeCell ref="A24:X24"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A15:X15"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="V35:X35"/>
-    <mergeCell ref="M1:X1"/>
-    <mergeCell ref="U43:X43"/>
-    <mergeCell ref="A42:J42"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G8:X8"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/web/public/forms/gy-nda.xlsx
+++ b/web/public/forms/gy-nda.xlsx
@@ -581,7 +581,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
